--- a/data.xlsx
+++ b/data.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="产品信息与Milestone" sheetId="2" r:id="rId4"/>
+    <sheet name="推送排期表" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
@@ -1368,4 +1369,832 @@
     </dataValidation>
   </dataValidations>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="13" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>期数</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>推送日期</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>星期</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>负责产品</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>推送主题</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>稿件状态</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>提醒日期</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25.5" customHeight="1">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PorosHoster</t>
+        </is>
+      </c>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="H2" s="2">
+        <v>46118</v>
+      </c>
+      <c r="I2"/>
+    </row>
+    <row r="3" ht="25.5" customHeight="1">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PorosAgent-MDagent</t>
+        </is>
+      </c>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H3" s="2">
+        <v>46121</v>
+      </c>
+      <c r="I3"/>
+    </row>
+    <row r="4" ht="25.5" customHeight="1">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46126</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PorosMGE</t>
+        </is>
+      </c>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H4" s="2">
+        <v>46125</v>
+      </c>
+      <c r="I4"/>
+    </row>
+    <row r="5" ht="25.5" customHeight="1">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PorosAgent-SchwarzXtal</t>
+        </is>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H5" s="2">
+        <v>46128</v>
+      </c>
+      <c r="I5"/>
+    </row>
+    <row r="6" ht="25.5" customHeight="1">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46133</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PorosMatterNets</t>
+        </is>
+      </c>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H6" s="2">
+        <v>46132</v>
+      </c>
+      <c r="I6"/>
+    </row>
+    <row r="7" ht="25.5" customHeight="1">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PorosDataProcessor</t>
+        </is>
+      </c>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H7" s="2">
+        <v>46135</v>
+      </c>
+      <c r="I7"/>
+    </row>
+    <row r="8" ht="25.5" customHeight="1">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PorosMatterDatabase</t>
+        </is>
+      </c>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H8" s="2">
+        <v>46139</v>
+      </c>
+      <c r="I8"/>
+    </row>
+    <row r="9" ht="25.5" customHeight="1">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46143</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PorosHoster</t>
+        </is>
+      </c>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H9" s="2">
+        <v>46142</v>
+      </c>
+      <c r="I9"/>
+    </row>
+    <row r="10" ht="25.5" customHeight="1">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>46147</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PorosAgent-MDagent</t>
+        </is>
+      </c>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H10" s="2">
+        <v>46146</v>
+      </c>
+      <c r="I10"/>
+    </row>
+    <row r="11" ht="25.5" customHeight="1">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PorosMGE</t>
+        </is>
+      </c>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H11" s="2">
+        <v>46149</v>
+      </c>
+      <c r="I11"/>
+    </row>
+    <row r="12" ht="25.5" customHeight="1">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>46154</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PorosAgent-SchwarzXtal</t>
+        </is>
+      </c>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H12" s="2">
+        <v>46153</v>
+      </c>
+      <c r="I12"/>
+    </row>
+    <row r="13" ht="25.5" customHeight="1">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PorosMatterNets</t>
+        </is>
+      </c>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H13" s="2">
+        <v>46156</v>
+      </c>
+      <c r="I13"/>
+    </row>
+    <row r="14" ht="25.5" customHeight="1">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>46161</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PorosDataProcessor</t>
+        </is>
+      </c>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H14" s="2">
+        <v>46160</v>
+      </c>
+      <c r="I14"/>
+    </row>
+    <row r="15" ht="25.5" customHeight="1">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PorosMatterDatabase</t>
+        </is>
+      </c>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H15" s="2">
+        <v>46163</v>
+      </c>
+      <c r="I15"/>
+    </row>
+    <row r="16" ht="25.5" customHeight="1">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PorosHoster</t>
+        </is>
+      </c>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H16" s="2">
+        <v>46167</v>
+      </c>
+      <c r="I16"/>
+    </row>
+    <row r="17" ht="25.5" customHeight="1">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PorosAgent-MDagent</t>
+        </is>
+      </c>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H17" s="2">
+        <v>46170</v>
+      </c>
+      <c r="I17"/>
+    </row>
+    <row r="18" ht="25.5" customHeight="1">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2">
+        <v>46175</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PorosMGE</t>
+        </is>
+      </c>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H18" s="2">
+        <v>46174</v>
+      </c>
+      <c r="I18"/>
+    </row>
+    <row r="19" ht="25.5" customHeight="1">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2">
+        <v>46178</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PorosAgent-SchwarzXtal</t>
+        </is>
+      </c>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H19" s="2">
+        <v>46177</v>
+      </c>
+      <c r="I19"/>
+    </row>
+    <row r="20" ht="25.5" customHeight="1">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
+        <v>46182</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PorosMatterNets</t>
+        </is>
+      </c>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H20" s="2">
+        <v>46181</v>
+      </c>
+      <c r="I20"/>
+    </row>
+    <row r="21" ht="25.5" customHeight="1">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>46185</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PorosDataProcessor</t>
+        </is>
+      </c>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H21" s="2">
+        <v>46184</v>
+      </c>
+      <c r="I21"/>
+    </row>
+    <row r="22" ht="25.5" customHeight="1">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
+        <v>46189</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PorosMatterDatabase</t>
+        </is>
+      </c>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H22" s="2">
+        <v>46188</v>
+      </c>
+      <c r="I22"/>
+    </row>
+    <row r="23" ht="25.5" customHeight="1">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PorosHoster</t>
+        </is>
+      </c>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H23" s="2">
+        <v>46191</v>
+      </c>
+      <c r="I23"/>
+    </row>
+    <row r="24" ht="25.5" customHeight="1">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2">
+        <v>46196</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PorosAgent-MDagent</t>
+        </is>
+      </c>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H24" s="2">
+        <v>46195</v>
+      </c>
+      <c r="I24"/>
+    </row>
+    <row r="25" ht="25.5" customHeight="1">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PorosMGE</t>
+        </is>
+      </c>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H25" s="2">
+        <v>46198</v>
+      </c>
+      <c r="I25"/>
+    </row>
+    <row r="26" ht="25.5" customHeight="1">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PorosAgent-SchwarzXtal</t>
+        </is>
+      </c>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H26" s="2">
+        <v>46202</v>
+      </c>
+      <c r="I26"/>
+    </row>
+    <row r="27" ht="25.5" customHeight="1">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PorosMatterNets</t>
+        </is>
+      </c>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="H27" s="2">
+        <v>46205</v>
+      </c>
+      <c r="I27"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation allowBlank="false" sqref="C2:C26" type="list">
+      <formula1>"周二,周五"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="false" sqref="G2:G26" type="list">
+      <formula1>"未开始,撰写中,已提交,已审核,已发布"</formula1>
+    </dataValidation>
+  </dataValidations>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="产品信息与Milestone" sheetId="2" r:id="rId4"/>
-    <sheet name="推送排期表" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
@@ -1369,832 +1368,4 @@
     </dataValidation>
   </dataValidations>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="13" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>期数</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>推送日期</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>星期</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>负责产品</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>负责人</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>推送主题</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>稿件状态</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>提醒日期</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="25.5" customHeight="1">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2">
-        <v>46119</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>周二</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>PorosHoster</t>
-        </is>
-      </c>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>已发布</t>
-        </is>
-      </c>
-      <c r="H2" s="2">
-        <v>46118</v>
-      </c>
-      <c r="I2"/>
-    </row>
-    <row r="3" ht="25.5" customHeight="1">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2">
-        <v>46122</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>PorosAgent-MDagent</t>
-        </is>
-      </c>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H3" s="2">
-        <v>46121</v>
-      </c>
-      <c r="I3"/>
-    </row>
-    <row r="4" ht="25.5" customHeight="1">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2">
-        <v>46126</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>周二</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>PorosMGE</t>
-        </is>
-      </c>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H4" s="2">
-        <v>46125</v>
-      </c>
-      <c r="I4"/>
-    </row>
-    <row r="5" ht="25.5" customHeight="1">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2">
-        <v>46129</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>PorosAgent-SchwarzXtal</t>
-        </is>
-      </c>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H5" s="2">
-        <v>46128</v>
-      </c>
-      <c r="I5"/>
-    </row>
-    <row r="6" ht="25.5" customHeight="1">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2">
-        <v>46133</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>周二</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>PorosMatterNets</t>
-        </is>
-      </c>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H6" s="2">
-        <v>46132</v>
-      </c>
-      <c r="I6"/>
-    </row>
-    <row r="7" ht="25.5" customHeight="1">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2">
-        <v>46136</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>PorosDataProcessor</t>
-        </is>
-      </c>
-      <c r="E7"/>
-      <c r="F7"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H7" s="2">
-        <v>46135</v>
-      </c>
-      <c r="I7"/>
-    </row>
-    <row r="8" ht="25.5" customHeight="1">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2">
-        <v>46140</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>周二</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PorosMatterDatabase</t>
-        </is>
-      </c>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H8" s="2">
-        <v>46139</v>
-      </c>
-      <c r="I8"/>
-    </row>
-    <row r="9" ht="25.5" customHeight="1">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2">
-        <v>46143</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PorosHoster</t>
-        </is>
-      </c>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H9" s="2">
-        <v>46142</v>
-      </c>
-      <c r="I9"/>
-    </row>
-    <row r="10" ht="25.5" customHeight="1">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2">
-        <v>46147</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>周二</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PorosAgent-MDagent</t>
-        </is>
-      </c>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H10" s="2">
-        <v>46146</v>
-      </c>
-      <c r="I10"/>
-    </row>
-    <row r="11" ht="25.5" customHeight="1">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2">
-        <v>46150</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>PorosMGE</t>
-        </is>
-      </c>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H11" s="2">
-        <v>46149</v>
-      </c>
-      <c r="I11"/>
-    </row>
-    <row r="12" ht="25.5" customHeight="1">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2">
-        <v>46154</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>周二</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>PorosAgent-SchwarzXtal</t>
-        </is>
-      </c>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H12" s="2">
-        <v>46153</v>
-      </c>
-      <c r="I12"/>
-    </row>
-    <row r="13" ht="25.5" customHeight="1">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2">
-        <v>46157</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>PorosMatterNets</t>
-        </is>
-      </c>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H13" s="2">
-        <v>46156</v>
-      </c>
-      <c r="I13"/>
-    </row>
-    <row r="14" ht="25.5" customHeight="1">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2">
-        <v>46161</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>周二</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PorosDataProcessor</t>
-        </is>
-      </c>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H14" s="2">
-        <v>46160</v>
-      </c>
-      <c r="I14"/>
-    </row>
-    <row r="15" ht="25.5" customHeight="1">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2">
-        <v>46164</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>PorosMatterDatabase</t>
-        </is>
-      </c>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H15" s="2">
-        <v>46163</v>
-      </c>
-      <c r="I15"/>
-    </row>
-    <row r="16" ht="25.5" customHeight="1">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2">
-        <v>46168</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>周二</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>PorosHoster</t>
-        </is>
-      </c>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H16" s="2">
-        <v>46167</v>
-      </c>
-      <c r="I16"/>
-    </row>
-    <row r="17" ht="25.5" customHeight="1">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2">
-        <v>46171</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>PorosAgent-MDagent</t>
-        </is>
-      </c>
-      <c r="E17"/>
-      <c r="F17"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H17" s="2">
-        <v>46170</v>
-      </c>
-      <c r="I17"/>
-    </row>
-    <row r="18" ht="25.5" customHeight="1">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2">
-        <v>46175</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>周二</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>PorosMGE</t>
-        </is>
-      </c>
-      <c r="E18"/>
-      <c r="F18"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H18" s="2">
-        <v>46174</v>
-      </c>
-      <c r="I18"/>
-    </row>
-    <row r="19" ht="25.5" customHeight="1">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2">
-        <v>46178</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>PorosAgent-SchwarzXtal</t>
-        </is>
-      </c>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H19" s="2">
-        <v>46177</v>
-      </c>
-      <c r="I19"/>
-    </row>
-    <row r="20" ht="25.5" customHeight="1">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2">
-        <v>46182</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>周二</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>PorosMatterNets</t>
-        </is>
-      </c>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H20" s="2">
-        <v>46181</v>
-      </c>
-      <c r="I20"/>
-    </row>
-    <row r="21" ht="25.5" customHeight="1">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2">
-        <v>46185</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>PorosDataProcessor</t>
-        </is>
-      </c>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H21" s="2">
-        <v>46184</v>
-      </c>
-      <c r="I21"/>
-    </row>
-    <row r="22" ht="25.5" customHeight="1">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2">
-        <v>46189</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>周二</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>PorosMatterDatabase</t>
-        </is>
-      </c>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H22" s="2">
-        <v>46188</v>
-      </c>
-      <c r="I22"/>
-    </row>
-    <row r="23" ht="25.5" customHeight="1">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2">
-        <v>46192</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>PorosHoster</t>
-        </is>
-      </c>
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H23" s="2">
-        <v>46191</v>
-      </c>
-      <c r="I23"/>
-    </row>
-    <row r="24" ht="25.5" customHeight="1">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2">
-        <v>46196</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>周二</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>PorosAgent-MDagent</t>
-        </is>
-      </c>
-      <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H24" s="2">
-        <v>46195</v>
-      </c>
-      <c r="I24"/>
-    </row>
-    <row r="25" ht="25.5" customHeight="1">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2">
-        <v>46199</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>PorosMGE</t>
-        </is>
-      </c>
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H25" s="2">
-        <v>46198</v>
-      </c>
-      <c r="I25"/>
-    </row>
-    <row r="26" ht="25.5" customHeight="1">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2">
-        <v>46203</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>周二</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>PorosAgent-SchwarzXtal</t>
-        </is>
-      </c>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H26" s="2">
-        <v>46202</v>
-      </c>
-      <c r="I26"/>
-    </row>
-    <row r="27" ht="25.5" customHeight="1">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2">
-        <v>46206</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>PorosMatterNets</t>
-        </is>
-      </c>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="H27" s="2">
-        <v>46205</v>
-      </c>
-      <c r="I27"/>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation allowBlank="false" sqref="C2:C26" type="list">
-      <formula1>"周二,周五"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="false" sqref="G2:G26" type="list">
-      <formula1>"未开始,撰写中,已提交,已审核,已发布"</formula1>
-    </dataValidation>
-  </dataValidations>
-</worksheet>
 </file>